--- a/WebAppEstimate/Areas/SiteBram/ExcelFileLoad/WinchAnchorExcel/WinchAnchorTest.xlsx
+++ b/WebAppEstimate/Areas/SiteBram/ExcelFileLoad/WinchAnchorExcel/WinchAnchorTest.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Series" sheetId="5" r:id="rId1"/>
     <sheet name="Weight" sheetId="2" r:id="rId2"/>
     <sheet name="Shaft" sheetId="3" r:id="rId3"/>
     <sheet name="Chain" sheetId="4" r:id="rId4"/>
-    <sheet name="List1" sheetId="1" r:id="rId5"/>
+    <sheet name="Design" sheetId="6" r:id="rId5"/>
+    <sheet name="List1" sheetId="1" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="18">
   <si>
     <t>weight</t>
   </si>
@@ -61,20 +62,29 @@
     <t>Hour</t>
   </si>
   <si>
-    <t>Id</t>
-  </si>
-  <si>
     <t>ValueMm</t>
   </si>
   <si>
     <t>ValueKgMm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ValueKg </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ValueMm </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ValueKgMm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +138,13 @@
       <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Cascadia Code"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Hasklig"/>
       <family val="3"/>
       <charset val="204"/>
     </font>
@@ -232,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -243,9 +260,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -259,6 +273,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -539,252 +558,279 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="11"/>
-    <col min="3" max="3" width="15.7109375" style="11" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="18.5703125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="10"/>
+    <col min="3" max="3" width="15.7109375" style="10" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="11" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="11">
-        <v>1</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="11">
-        <v>2</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="11">
-        <v>3</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="11">
-        <v>4</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" s="11">
-        <v>5</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>6</v>
-      </c>
+      <c r="B1" s="23"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="23"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="23"/>
+      <c r="C3" s="11"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="11"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="11"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="23"/>
+      <c r="C6" s="11"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="11"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:K47"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="11"/>
-    <col min="2" max="2" width="18.42578125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="11" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="19.42578125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="18" style="10" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="10" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="18">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="17">
         <v>1000</v>
       </c>
-      <c r="D3" s="18">
+      <c r="C2" s="17">
         <v>100.25</v>
       </c>
-      <c r="F3" s="12"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17">
+        <v>1500</v>
+      </c>
+      <c r="C3" s="17">
+        <v>150.25</v>
+      </c>
+      <c r="D3" s="17"/>
+      <c r="F3" s="11"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="18">
-        <v>1500</v>
-      </c>
-      <c r="D4" s="18">
-        <v>150.25</v>
-      </c>
-      <c r="F4" s="12"/>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17">
+        <v>2000</v>
+      </c>
+      <c r="C4" s="17">
+        <v>200.25</v>
+      </c>
+      <c r="D4" s="17"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="18">
-        <v>2000</v>
-      </c>
-      <c r="D5" s="18">
-        <v>200.25</v>
-      </c>
-      <c r="F5" s="12"/>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17">
+        <v>2500</v>
+      </c>
+      <c r="C5" s="17">
+        <v>250.25</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="F5" s="11"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="18">
-        <v>2500</v>
-      </c>
-      <c r="D6" s="18">
-        <v>250.25</v>
-      </c>
-      <c r="F6" s="12"/>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17">
+        <v>3000</v>
+      </c>
+      <c r="C6" s="17">
+        <v>300.25</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="F6" s="11"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="18">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="17">
+        <v>3500</v>
+      </c>
+      <c r="C7" s="17">
+        <v>350.25</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="17">
+        <v>4000</v>
+      </c>
+      <c r="C8" s="17">
+        <v>400.25</v>
+      </c>
+      <c r="D8" s="17"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17">
+        <v>4500</v>
+      </c>
+      <c r="C9" s="17">
+        <v>450.25</v>
+      </c>
+      <c r="D9" s="17"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="17">
+        <v>5000</v>
+      </c>
+      <c r="C10" s="17">
+        <v>500.25</v>
+      </c>
+      <c r="D10" s="17"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="20">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="20">
+        <v>110.25</v>
+      </c>
+      <c r="D11" s="17"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="20">
+        <v>1500</v>
+      </c>
+      <c r="C12" s="20">
+        <v>160.25</v>
+      </c>
+      <c r="D12" s="20"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="20">
+        <v>2000</v>
+      </c>
+      <c r="C13" s="20">
+        <v>210.25</v>
+      </c>
+      <c r="D13" s="20"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="20">
+        <v>2500</v>
+      </c>
+      <c r="C14" s="20">
+        <v>260.25</v>
+      </c>
+      <c r="D14" s="20"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="20">
         <v>3000</v>
       </c>
-      <c r="D7" s="18">
-        <v>300.25</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="18">
-        <v>3500</v>
-      </c>
-      <c r="D8" s="18">
-        <v>350.25</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="18">
-        <v>4000</v>
-      </c>
-      <c r="D9" s="18">
-        <v>400.25</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="18">
-        <v>4500</v>
-      </c>
-      <c r="D10" s="18">
-        <v>450.25</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="18">
-        <v>5000</v>
-      </c>
-      <c r="D11" s="18">
-        <v>500.25</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="21">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="21">
-        <v>110.25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="21">
-        <v>1500</v>
-      </c>
-      <c r="D13" s="21">
-        <v>160.25</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="21">
-        <v>2000</v>
-      </c>
-      <c r="D14" s="21">
-        <v>210.25</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="21">
-        <v>2500</v>
-      </c>
-      <c r="D15" s="21">
-        <v>260.25</v>
-      </c>
+      <c r="C15" s="20">
+        <v>310.25</v>
+      </c>
+      <c r="D15" s="20"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -793,357 +839,382 @@
       <c r="J15" s="5"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="21">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="20">
+        <v>3500</v>
+      </c>
+      <c r="C16" s="20">
+        <v>360.25</v>
+      </c>
+      <c r="D16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="20">
+        <v>4000</v>
+      </c>
+      <c r="C17" s="20">
+        <v>410.25</v>
+      </c>
+      <c r="D17" s="20"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="20">
+        <v>4500</v>
+      </c>
+      <c r="C18" s="20">
+        <v>460.25</v>
+      </c>
+      <c r="D18" s="20"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="20">
+        <v>5000</v>
+      </c>
+      <c r="C19" s="20">
+        <v>510.25</v>
+      </c>
+      <c r="D19" s="20"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="19">
+        <v>1000</v>
+      </c>
+      <c r="C20" s="19">
+        <v>120.25</v>
+      </c>
+      <c r="D20" s="20"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="19">
+        <v>1500</v>
+      </c>
+      <c r="C21" s="19">
+        <v>170.25</v>
+      </c>
+      <c r="D21" s="19"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="19">
+        <v>2000</v>
+      </c>
+      <c r="C22" s="19">
+        <v>220.25</v>
+      </c>
+      <c r="D22" s="19"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19">
+        <v>2500</v>
+      </c>
+      <c r="C23" s="19">
+        <v>270.25</v>
+      </c>
+      <c r="D23" s="19"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="19">
         <v>3000</v>
       </c>
-      <c r="D16" s="21">
-        <v>310.25</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="21">
+      <c r="C24" s="19">
+        <v>320.25</v>
+      </c>
+      <c r="D24" s="19"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19">
         <v>3500</v>
       </c>
-      <c r="D17" s="21">
-        <v>360.25</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="21">
+      <c r="C25" s="19">
+        <v>370.25</v>
+      </c>
+      <c r="D25" s="19"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="19">
         <v>4000</v>
       </c>
-      <c r="D18" s="21">
-        <v>410.25</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="21">
+      <c r="C26" s="19">
+        <v>420.25</v>
+      </c>
+      <c r="D26" s="19"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="19">
         <v>4500</v>
       </c>
-      <c r="D19" s="21">
-        <v>460.25</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="21">
+      <c r="C27" s="19">
+        <v>470.25</v>
+      </c>
+      <c r="D27" s="19"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="19">
         <v>5000</v>
       </c>
-      <c r="D20" s="21">
-        <v>510.25</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B21" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="20">
+      <c r="C28" s="19">
+        <v>520.25</v>
+      </c>
+      <c r="D28" s="19"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="18">
         <v>1000</v>
       </c>
-      <c r="D21" s="20">
-        <v>120.25</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="20">
+      <c r="C29" s="18">
+        <v>130.25</v>
+      </c>
+      <c r="D29" s="19"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="18">
         <v>1500</v>
       </c>
-      <c r="D22" s="20">
-        <v>170.25</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="20">
+      <c r="C30" s="18">
+        <v>180.25</v>
+      </c>
+      <c r="D30" s="18"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="18">
         <v>2000</v>
       </c>
-      <c r="D23" s="20">
-        <v>220.25</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="20">
+      <c r="C31" s="18">
+        <v>230.25</v>
+      </c>
+      <c r="D31" s="18"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="18">
         <v>2500</v>
       </c>
-      <c r="D24" s="20">
-        <v>270.25</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="20">
+      <c r="C32" s="18">
+        <v>280.25</v>
+      </c>
+      <c r="D32" s="18"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="18">
         <v>3000</v>
       </c>
-      <c r="D25" s="20">
-        <v>320.25</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B26" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="20">
+      <c r="C33" s="18">
+        <v>330.25</v>
+      </c>
+      <c r="D33" s="18"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="18">
         <v>3500</v>
       </c>
-      <c r="D26" s="20">
-        <v>370.25</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="20">
+      <c r="C34" s="18">
+        <v>380.25</v>
+      </c>
+      <c r="D34" s="18"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="18">
         <v>4000</v>
       </c>
-      <c r="D27" s="20">
-        <v>420.25</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="20">
+      <c r="C35" s="18">
+        <v>430.25</v>
+      </c>
+      <c r="D35" s="18"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="18">
         <v>4500</v>
       </c>
-      <c r="D28" s="20">
-        <v>470.25</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B29" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="20">
+      <c r="C36" s="18">
+        <v>480.25</v>
+      </c>
+      <c r="D36" s="18"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="18">
         <v>5000</v>
       </c>
-      <c r="D29" s="20">
-        <v>520.25</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B30" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="19">
+      <c r="C37" s="18">
+        <v>530.25</v>
+      </c>
+      <c r="D37" s="18"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="21">
         <v>1000</v>
       </c>
-      <c r="D30" s="19">
-        <v>130.25</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="19">
+      <c r="C38" s="21">
+        <v>140.25</v>
+      </c>
+      <c r="D38" s="18"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="21">
         <v>1500</v>
       </c>
-      <c r="D31" s="19">
-        <v>180.25</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="19">
+      <c r="C39" s="21">
+        <v>190.25</v>
+      </c>
+      <c r="D39" s="21"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="21">
         <v>2000</v>
       </c>
-      <c r="D32" s="19">
-        <v>230.25</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B33" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="19">
+      <c r="C40" s="21">
+        <v>240.25</v>
+      </c>
+      <c r="D40" s="21"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="21">
         <v>2500</v>
       </c>
-      <c r="D33" s="19">
-        <v>280.25</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B34" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="19">
+      <c r="C41" s="21">
+        <v>290.25</v>
+      </c>
+      <c r="D41" s="21"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="21">
         <v>3000</v>
       </c>
-      <c r="D34" s="19">
-        <v>330.25</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B35" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="19">
+      <c r="C42" s="21">
+        <v>340.25</v>
+      </c>
+      <c r="D42" s="21"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="21">
         <v>3500</v>
       </c>
-      <c r="D35" s="19">
-        <v>380.25</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B36" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="19">
+      <c r="C43" s="21">
+        <v>390.25</v>
+      </c>
+      <c r="D43" s="21"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="21">
         <v>4000</v>
       </c>
-      <c r="D36" s="19">
-        <v>430.25</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B37" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="19">
+      <c r="C44" s="21">
+        <v>440.25</v>
+      </c>
+      <c r="D44" s="21"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="21">
         <v>4500</v>
       </c>
-      <c r="D37" s="19">
-        <v>480.25</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B38" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="19">
+      <c r="C45" s="21">
+        <v>490.25</v>
+      </c>
+      <c r="D45" s="21"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="21">
         <v>5000</v>
       </c>
-      <c r="D38" s="19">
-        <v>530.25</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B39" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="22">
-        <v>1000</v>
-      </c>
-      <c r="D39" s="22">
-        <v>140.25</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B40" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="22">
-        <v>1500</v>
-      </c>
-      <c r="D40" s="22">
-        <v>190.25</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="22">
-        <v>2000</v>
-      </c>
-      <c r="D41" s="22">
-        <v>240.25</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B42" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="22">
-        <v>2500</v>
-      </c>
-      <c r="D42" s="22">
-        <v>290.25</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B43" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="22">
-        <v>3000</v>
-      </c>
-      <c r="D43" s="22">
-        <v>340.25</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B44" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="22">
-        <v>3500</v>
-      </c>
-      <c r="D44" s="22">
-        <v>390.25</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B45" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="22">
-        <v>4000</v>
-      </c>
-      <c r="D45" s="22">
-        <v>440.25</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B46" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="22">
-        <v>4500</v>
-      </c>
-      <c r="D46" s="22">
-        <v>490.25</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B47" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="22">
-        <v>5000</v>
-      </c>
-      <c r="D47" s="22">
+      <c r="C46" s="21">
         <v>540.25</v>
       </c>
+      <c r="D46" s="21"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B47" s="12"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1153,519 +1224,570 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D47"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="11" t="s">
+      <c r="B1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="18">
+    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="17">
         <v>100</v>
       </c>
-      <c r="D3" s="18">
+      <c r="C2" s="17">
         <v>100.35</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="18">
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17">
         <v>150</v>
       </c>
-      <c r="D4" s="18">
+      <c r="C3" s="17">
         <v>150.35</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="18">
+      <c r="D3" s="17"/>
+    </row>
+    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17">
         <v>200</v>
       </c>
-      <c r="D5" s="18">
+      <c r="C4" s="17">
         <v>200.35</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="18">
+      <c r="D4" s="17"/>
+    </row>
+    <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17">
         <v>250</v>
       </c>
-      <c r="D6" s="18">
+      <c r="C5" s="17">
         <v>250.35</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B7" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="18">
+      <c r="D5" s="17"/>
+    </row>
+    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17">
         <v>300</v>
       </c>
-      <c r="D7" s="18">
+      <c r="C6" s="17">
         <v>300.35000000000002</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="18">
+      <c r="D6" s="17"/>
+    </row>
+    <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="17">
         <v>350</v>
       </c>
-      <c r="D8" s="18">
+      <c r="C7" s="17">
         <v>350.35</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="18">
+      <c r="D7" s="17"/>
+    </row>
+    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="17">
         <v>400</v>
       </c>
-      <c r="D9" s="18">
+      <c r="C8" s="17">
         <v>400.35</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="18">
+      <c r="D8" s="17"/>
+    </row>
+    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17">
         <v>450</v>
       </c>
-      <c r="D10" s="18">
+      <c r="C9" s="17">
         <v>450.35</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="18">
+      <c r="D9" s="17"/>
+    </row>
+    <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="17">
         <v>500</v>
       </c>
-      <c r="D11" s="18">
+      <c r="C10" s="17">
         <v>500.35</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B12" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="21">
+      <c r="D10" s="17"/>
+    </row>
+    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="20">
         <v>100</v>
       </c>
-      <c r="D12" s="21">
+      <c r="C11" s="20">
         <v>150.35</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="21">
+      <c r="D11" s="17"/>
+    </row>
+    <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="20">
         <v>150</v>
       </c>
-      <c r="D13" s="21">
+      <c r="C12" s="20">
         <v>200.35</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="21">
+      <c r="D12" s="20"/>
+    </row>
+    <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="20">
         <v>200</v>
       </c>
-      <c r="D14" s="21">
+      <c r="C13" s="20">
         <v>250.35</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="21">
+      <c r="D13" s="20"/>
+    </row>
+    <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="20">
         <v>250</v>
       </c>
-      <c r="D15" s="21">
+      <c r="C14" s="20">
         <v>300.35000000000002</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="21">
+      <c r="D14" s="20"/>
+    </row>
+    <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="20">
         <v>300</v>
       </c>
-      <c r="D16" s="21">
+      <c r="C15" s="20">
         <v>350.35</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="21">
+      <c r="D15" s="20"/>
+    </row>
+    <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="20">
         <v>350</v>
       </c>
-      <c r="D17" s="21">
+      <c r="C16" s="20">
         <v>400.35</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="21">
+      <c r="D16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="20">
         <v>400</v>
       </c>
-      <c r="D18" s="21">
+      <c r="C17" s="20">
         <v>450.35</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B19" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="21">
+      <c r="D17" s="20"/>
+    </row>
+    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="20">
         <v>450</v>
       </c>
-      <c r="D19" s="21">
+      <c r="C18" s="20">
         <v>500.35</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="21">
+      <c r="D18" s="20"/>
+    </row>
+    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="20">
         <v>500</v>
       </c>
-      <c r="D20" s="21">
+      <c r="C19" s="20">
         <v>550.35</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="20">
+      <c r="D19" s="20"/>
+    </row>
+    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="19">
         <v>100</v>
       </c>
-      <c r="D21" s="20">
+      <c r="C20" s="19">
         <v>200.35</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="20">
+      <c r="D20" s="20"/>
+    </row>
+    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="19">
         <v>150</v>
       </c>
-      <c r="D22" s="20">
+      <c r="C21" s="19">
         <v>250.35</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="20">
+      <c r="D21" s="19"/>
+    </row>
+    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="19">
         <v>200</v>
       </c>
-      <c r="D23" s="20">
+      <c r="C22" s="19">
         <v>300.35000000000002</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B24" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="20">
+      <c r="D22" s="19"/>
+    </row>
+    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19">
         <v>250</v>
       </c>
-      <c r="D24" s="20">
+      <c r="C23" s="19">
         <v>350.35</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="20">
+      <c r="D23" s="19"/>
+    </row>
+    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="19">
         <v>300</v>
       </c>
-      <c r="D25" s="20">
+      <c r="C24" s="19">
         <v>400.35</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B26" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="20">
+      <c r="D24" s="19"/>
+    </row>
+    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19">
         <v>350</v>
       </c>
-      <c r="D26" s="20">
+      <c r="C25" s="19">
         <v>450.35</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B27" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="20">
+      <c r="D25" s="19"/>
+    </row>
+    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="19">
         <v>400</v>
       </c>
-      <c r="D27" s="20">
+      <c r="C26" s="19">
         <v>500.35</v>
       </c>
-    </row>
-    <row r="28" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B28" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="20">
+      <c r="D26" s="19"/>
+    </row>
+    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="19">
         <v>450</v>
       </c>
-      <c r="D28" s="20">
+      <c r="C27" s="19">
         <v>550.35</v>
       </c>
-    </row>
-    <row r="29" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B29" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="20">
+      <c r="D27" s="19"/>
+    </row>
+    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="19">
         <v>500</v>
       </c>
-      <c r="D29" s="20">
+      <c r="C28" s="19">
         <v>600.35</v>
       </c>
-    </row>
-    <row r="30" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B30" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="19">
+      <c r="D28" s="19"/>
+    </row>
+    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="18">
         <v>100</v>
       </c>
-      <c r="D30" s="19">
+      <c r="C29" s="18">
         <v>250.35</v>
       </c>
-    </row>
-    <row r="31" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B31" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="19">
+      <c r="D29" s="19"/>
+    </row>
+    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="18">
         <v>150</v>
       </c>
-      <c r="D31" s="19">
+      <c r="C30" s="18">
         <v>300.35000000000002</v>
       </c>
-    </row>
-    <row r="32" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B32" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="19">
+      <c r="D30" s="18"/>
+    </row>
+    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="18">
         <v>200</v>
       </c>
-      <c r="D32" s="19">
+      <c r="C31" s="18">
         <v>350.35</v>
       </c>
-    </row>
-    <row r="33" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B33" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="19">
+      <c r="D31" s="18"/>
+    </row>
+    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="18">
         <v>250</v>
       </c>
-      <c r="D33" s="19">
+      <c r="C32" s="18">
         <v>400.35</v>
       </c>
-    </row>
-    <row r="34" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B34" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="19">
+      <c r="D32" s="18"/>
+    </row>
+    <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="18">
         <v>300</v>
       </c>
-      <c r="D34" s="19">
+      <c r="C33" s="18">
         <v>450.35</v>
       </c>
-    </row>
-    <row r="35" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B35" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="19">
+      <c r="D33" s="18"/>
+    </row>
+    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="18">
         <v>350</v>
       </c>
-      <c r="D35" s="19">
+      <c r="C34" s="18">
         <v>500.35</v>
       </c>
-    </row>
-    <row r="36" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B36" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="19">
+      <c r="D34" s="18"/>
+    </row>
+    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="18">
         <v>400</v>
       </c>
-      <c r="D36" s="19">
+      <c r="C35" s="18">
         <v>550.35</v>
       </c>
-    </row>
-    <row r="37" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B37" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="19">
+      <c r="D35" s="18"/>
+    </row>
+    <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="18">
         <v>450</v>
       </c>
-      <c r="D37" s="19">
+      <c r="C36" s="18">
         <v>600.35</v>
       </c>
-    </row>
-    <row r="38" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B38" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="19">
+      <c r="D36" s="18"/>
+    </row>
+    <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="18">
         <v>500</v>
       </c>
-      <c r="D38" s="19">
+      <c r="C37" s="18">
         <v>650.35</v>
       </c>
-    </row>
-    <row r="39" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B39" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="22">
+      <c r="D37" s="18"/>
+    </row>
+    <row r="38" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="21">
         <v>100</v>
       </c>
-      <c r="D39" s="22">
+      <c r="C38" s="21">
         <v>300.35000000000002</v>
       </c>
-    </row>
-    <row r="40" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B40" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="22">
+      <c r="D38" s="18"/>
+    </row>
+    <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="21">
         <v>150</v>
       </c>
-      <c r="D40" s="22">
+      <c r="C39" s="21">
         <v>350.35</v>
       </c>
-    </row>
-    <row r="41" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B41" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="22">
+      <c r="D39" s="21"/>
+    </row>
+    <row r="40" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="21">
         <v>200</v>
       </c>
-      <c r="D41" s="22">
+      <c r="C40" s="21">
         <v>400.35</v>
       </c>
-    </row>
-    <row r="42" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B42" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="22">
+      <c r="D40" s="21"/>
+    </row>
+    <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="21">
         <v>250</v>
       </c>
-      <c r="D42" s="22">
+      <c r="C41" s="21">
         <v>450.35</v>
       </c>
-    </row>
-    <row r="43" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B43" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="22">
+      <c r="D41" s="21"/>
+    </row>
+    <row r="42" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A42" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="21">
         <v>300</v>
       </c>
-      <c r="D43" s="22">
+      <c r="C42" s="21">
         <v>500.35</v>
       </c>
-    </row>
-    <row r="44" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B44" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="22">
+      <c r="D42" s="21"/>
+    </row>
+    <row r="43" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="21">
         <v>350</v>
       </c>
-      <c r="D44" s="22">
+      <c r="C43" s="21">
         <v>550.35</v>
       </c>
-    </row>
-    <row r="45" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B45" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="22">
+      <c r="D43" s="21"/>
+    </row>
+    <row r="44" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="21">
         <v>400</v>
       </c>
-      <c r="D45" s="22">
+      <c r="C44" s="21">
         <v>600.35</v>
       </c>
-    </row>
-    <row r="46" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B46" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="22">
+      <c r="D44" s="21"/>
+    </row>
+    <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A45" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="21">
         <v>450</v>
       </c>
-      <c r="D46" s="22">
+      <c r="C45" s="21">
         <v>650.35</v>
       </c>
-    </row>
-    <row r="47" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B47" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="22">
+      <c r="D45" s="21"/>
+    </row>
+    <row r="46" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="21">
         <v>500</v>
       </c>
-      <c r="D47" s="22">
+      <c r="C46" s="21">
         <v>700.35</v>
       </c>
+      <c r="D46" s="21"/>
+    </row>
+    <row r="47" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B47" s="12"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1674,519 +1796,570 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D47"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="13.5703125" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B2" s="11" t="s">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="11" t="s">
+      <c r="B1" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B3" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="18">
+    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="17">
         <v>22</v>
       </c>
-      <c r="D3" s="18">
+      <c r="C2" s="17">
         <v>220.22</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B4" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="18">
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17">
         <v>27</v>
       </c>
-      <c r="D4" s="18">
+      <c r="C3" s="17">
         <v>270.27</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B5" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="18">
+      <c r="D3" s="17"/>
+    </row>
+    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17">
         <v>32</v>
       </c>
-      <c r="D5" s="18">
+      <c r="C4" s="17">
         <v>320.32</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="18">
+      <c r="D4" s="17"/>
+    </row>
+    <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17">
         <v>37</v>
       </c>
-      <c r="D6" s="18">
+      <c r="C5" s="17">
         <v>370.37</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B7" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="18">
+      <c r="D5" s="17"/>
+    </row>
+    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17">
         <v>42</v>
       </c>
-      <c r="D7" s="18">
+      <c r="C6" s="17">
         <v>420.42</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="18">
+      <c r="D6" s="17"/>
+    </row>
+    <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="17">
         <v>47</v>
       </c>
-      <c r="D8" s="18">
+      <c r="C7" s="17">
         <v>470.47</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="18">
+      <c r="D7" s="17"/>
+    </row>
+    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="17">
         <v>52</v>
       </c>
-      <c r="D9" s="18">
+      <c r="C8" s="17">
         <v>520.52</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="18">
+      <c r="D8" s="17"/>
+    </row>
+    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17">
         <v>57</v>
       </c>
-      <c r="D10" s="18">
+      <c r="C9" s="17">
         <v>570.57000000000005</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="18">
+      <c r="D9" s="17"/>
+    </row>
+    <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="17">
         <v>62</v>
       </c>
-      <c r="D11" s="18">
+      <c r="C10" s="17">
         <v>620.62</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B12" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="21">
+      <c r="D10" s="17"/>
+    </row>
+    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="20">
         <v>22</v>
       </c>
-      <c r="D12" s="21">
+      <c r="C11" s="20">
         <v>222.25</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B13" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="21">
+      <c r="D11" s="17"/>
+    </row>
+    <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="20">
         <v>27</v>
       </c>
-      <c r="D13" s="21">
+      <c r="C12" s="20">
         <v>272.27</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B14" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="21">
+      <c r="D12" s="20"/>
+    </row>
+    <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="20">
         <v>32</v>
       </c>
-      <c r="D14" s="21">
+      <c r="C13" s="20">
         <v>322.29000000000002</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="21">
+      <c r="D13" s="20"/>
+    </row>
+    <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="20">
         <v>37</v>
       </c>
-      <c r="D15" s="21">
+      <c r="C14" s="20">
         <v>372.31</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="21">
+      <c r="D14" s="20"/>
+    </row>
+    <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="20">
         <v>42</v>
       </c>
-      <c r="D16" s="21">
+      <c r="C15" s="20">
         <v>422.33</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="21">
+      <c r="D15" s="20"/>
+    </row>
+    <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="20">
         <v>47</v>
       </c>
-      <c r="D17" s="21">
+      <c r="C16" s="20">
         <v>472.35</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B18" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="21">
+      <c r="D16" s="20"/>
+    </row>
+    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="20">
         <v>52</v>
       </c>
-      <c r="D18" s="21">
+      <c r="C17" s="20">
         <v>522.37</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B19" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="21">
+      <c r="D17" s="20"/>
+    </row>
+    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="20">
         <v>57</v>
       </c>
-      <c r="D19" s="21">
+      <c r="C18" s="20">
         <v>572.39</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="21">
+      <c r="D18" s="20"/>
+    </row>
+    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="20">
         <v>62</v>
       </c>
-      <c r="D20" s="21">
+      <c r="C19" s="20">
         <v>622.41</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="20">
+      <c r="D19" s="20"/>
+    </row>
+    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="19">
         <v>22</v>
       </c>
-      <c r="D21" s="20">
+      <c r="C20" s="19">
         <v>224.28</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="20">
+      <c r="D20" s="20"/>
+    </row>
+    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="19">
         <v>27</v>
       </c>
-      <c r="D22" s="20">
+      <c r="C21" s="19">
         <v>274.27</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="20">
+      <c r="D21" s="19"/>
+    </row>
+    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="19">
         <v>32</v>
       </c>
-      <c r="D23" s="20">
+      <c r="C22" s="19">
         <v>324.26</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B24" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="20">
+      <c r="D22" s="19"/>
+    </row>
+    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19">
         <v>37</v>
       </c>
-      <c r="D24" s="20">
+      <c r="C23" s="19">
         <v>374.25</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="20">
+      <c r="D23" s="19"/>
+    </row>
+    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="19">
         <v>42</v>
       </c>
-      <c r="D25" s="20">
+      <c r="C24" s="19">
         <v>424.24</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B26" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="20">
+      <c r="D24" s="19"/>
+    </row>
+    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19">
         <v>47</v>
       </c>
-      <c r="D26" s="20">
+      <c r="C25" s="19">
         <v>474.23</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B27" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="20">
+      <c r="D25" s="19"/>
+    </row>
+    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="19">
         <v>52</v>
       </c>
-      <c r="D27" s="20">
+      <c r="C26" s="19">
         <v>524.22</v>
       </c>
-    </row>
-    <row r="28" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B28" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="20">
+      <c r="D26" s="19"/>
+    </row>
+    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="19">
         <v>57</v>
       </c>
-      <c r="D28" s="20">
+      <c r="C27" s="19">
         <v>574.21</v>
       </c>
-    </row>
-    <row r="29" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B29" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="20">
+      <c r="D27" s="19"/>
+    </row>
+    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="19">
         <v>62</v>
       </c>
-      <c r="D29" s="23">
+      <c r="C28" s="22">
         <v>624.20000000000005</v>
       </c>
-    </row>
-    <row r="30" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B30" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="19">
+      <c r="D28" s="19"/>
+    </row>
+    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="18">
         <v>22</v>
       </c>
-      <c r="D30" s="19">
+      <c r="C29" s="18">
         <v>226.31</v>
       </c>
-    </row>
-    <row r="31" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B31" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="19">
+      <c r="D29" s="22"/>
+    </row>
+    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="18">
         <v>27</v>
       </c>
-      <c r="D31" s="19">
+      <c r="C30" s="18">
         <v>276.27</v>
       </c>
-    </row>
-    <row r="32" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B32" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32" s="19">
+      <c r="D30" s="18"/>
+    </row>
+    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="18">
         <v>32</v>
       </c>
-      <c r="D32" s="19">
+      <c r="C31" s="18">
         <v>326.23</v>
       </c>
-    </row>
-    <row r="33" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B33" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="19">
+      <c r="D31" s="18"/>
+    </row>
+    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="18">
         <v>37</v>
       </c>
-      <c r="D33" s="19">
+      <c r="C32" s="18">
         <v>376.19</v>
       </c>
-    </row>
-    <row r="34" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B34" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="19">
+      <c r="D32" s="18"/>
+    </row>
+    <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="18">
         <v>42</v>
       </c>
-      <c r="D34" s="19">
+      <c r="C33" s="18">
         <v>426.15</v>
       </c>
-    </row>
-    <row r="35" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B35" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="19">
+      <c r="D33" s="18"/>
+    </row>
+    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="18">
         <v>47</v>
       </c>
-      <c r="D35" s="19">
+      <c r="C34" s="18">
         <v>476.11</v>
       </c>
-    </row>
-    <row r="36" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B36" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="19">
+      <c r="D34" s="18"/>
+    </row>
+    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="18">
         <v>52</v>
       </c>
-      <c r="D36" s="19">
+      <c r="C35" s="18">
         <v>526.07000000000005</v>
       </c>
-    </row>
-    <row r="37" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B37" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="19">
+      <c r="D35" s="18"/>
+    </row>
+    <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="18">
         <v>57</v>
       </c>
-      <c r="D37" s="19">
+      <c r="C36" s="18">
         <v>576.03</v>
       </c>
-    </row>
-    <row r="38" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B38" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="19">
+      <c r="D36" s="18"/>
+    </row>
+    <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="18">
         <v>62</v>
       </c>
-      <c r="D38" s="19">
+      <c r="C37" s="18">
         <v>625.99</v>
       </c>
-    </row>
-    <row r="39" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B39" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="22">
+      <c r="D37" s="18"/>
+    </row>
+    <row r="38" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="21">
         <v>22</v>
       </c>
-      <c r="D39" s="22">
+      <c r="C38" s="21">
         <v>228.34</v>
       </c>
-    </row>
-    <row r="40" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B40" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="22">
+      <c r="D38" s="18"/>
+    </row>
+    <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="21">
         <v>27</v>
       </c>
-      <c r="D40" s="22">
+      <c r="C39" s="21">
         <v>278.27</v>
       </c>
-    </row>
-    <row r="41" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B41" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="22">
+      <c r="D39" s="21"/>
+    </row>
+    <row r="40" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="21">
         <v>32</v>
       </c>
-      <c r="D41" s="22">
+      <c r="C40" s="21">
         <v>328.2</v>
       </c>
-    </row>
-    <row r="42" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B42" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="22">
+      <c r="D40" s="21"/>
+    </row>
+    <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="21">
         <v>37</v>
       </c>
-      <c r="D42" s="22">
+      <c r="C41" s="21">
         <v>378.13</v>
       </c>
-    </row>
-    <row r="43" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B43" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="22">
+      <c r="D41" s="21"/>
+    </row>
+    <row r="42" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A42" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="21">
         <v>42</v>
       </c>
-      <c r="D43" s="22">
+      <c r="C42" s="21">
         <v>428.06</v>
       </c>
-    </row>
-    <row r="44" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B44" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="22">
+      <c r="D42" s="21"/>
+    </row>
+    <row r="43" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="21">
         <v>47</v>
       </c>
-      <c r="D44" s="22">
+      <c r="C43" s="21">
         <v>477.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B45" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="22">
+      <c r="D43" s="21"/>
+    </row>
+    <row r="44" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="21">
         <v>52</v>
       </c>
-      <c r="D45" s="22">
+      <c r="C44" s="21">
         <v>527.91999999999996</v>
       </c>
-    </row>
-    <row r="46" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B46" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="22">
+      <c r="D44" s="21"/>
+    </row>
+    <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A45" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="21">
         <v>57</v>
       </c>
-      <c r="D46" s="22">
+      <c r="C45" s="21">
         <v>577.85</v>
       </c>
-    </row>
-    <row r="47" spans="2:4" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B47" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="22">
+      <c r="D45" s="21"/>
+    </row>
+    <row r="46" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="21">
         <v>62</v>
       </c>
-      <c r="D47" s="22">
+      <c r="C46" s="21">
         <v>627.78</v>
       </c>
+      <c r="D46" s="21"/>
+    </row>
+    <row r="47" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B47" s="12"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2194,6 +2367,823 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="17">
+        <v>1000</v>
+      </c>
+      <c r="C2" s="17">
+        <v>100</v>
+      </c>
+      <c r="D2" s="17">
+        <v>22</v>
+      </c>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+    </row>
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17">
+        <v>1500</v>
+      </c>
+      <c r="C3" s="17">
+        <v>150</v>
+      </c>
+      <c r="D3" s="17">
+        <v>27</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+    </row>
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17">
+        <v>2000</v>
+      </c>
+      <c r="C4" s="17">
+        <v>200</v>
+      </c>
+      <c r="D4" s="17">
+        <v>32</v>
+      </c>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17">
+        <v>2500</v>
+      </c>
+      <c r="C5" s="17">
+        <v>250</v>
+      </c>
+      <c r="D5" s="17">
+        <v>37</v>
+      </c>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17">
+        <v>3000</v>
+      </c>
+      <c r="C6" s="17">
+        <v>300</v>
+      </c>
+      <c r="D6" s="17">
+        <v>42</v>
+      </c>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+    </row>
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="17">
+        <v>3500</v>
+      </c>
+      <c r="C7" s="17">
+        <v>350</v>
+      </c>
+      <c r="D7" s="17">
+        <v>47</v>
+      </c>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="17">
+        <v>4000</v>
+      </c>
+      <c r="C8" s="17">
+        <v>400</v>
+      </c>
+      <c r="D8" s="17">
+        <v>52</v>
+      </c>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+    </row>
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17">
+        <v>4500</v>
+      </c>
+      <c r="C9" s="17">
+        <v>450</v>
+      </c>
+      <c r="D9" s="17">
+        <v>57</v>
+      </c>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+    </row>
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="17">
+        <v>5000</v>
+      </c>
+      <c r="C10" s="17">
+        <v>500</v>
+      </c>
+      <c r="D10" s="17">
+        <v>62</v>
+      </c>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+    </row>
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="20">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="20">
+        <v>100</v>
+      </c>
+      <c r="D11" s="20">
+        <v>22</v>
+      </c>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+    </row>
+    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="20">
+        <v>1500</v>
+      </c>
+      <c r="C12" s="20">
+        <v>150</v>
+      </c>
+      <c r="D12" s="20">
+        <v>27</v>
+      </c>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+    </row>
+    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="20">
+        <v>2000</v>
+      </c>
+      <c r="C13" s="20">
+        <v>200</v>
+      </c>
+      <c r="D13" s="20">
+        <v>32</v>
+      </c>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+    </row>
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="20">
+        <v>2500</v>
+      </c>
+      <c r="C14" s="20">
+        <v>250</v>
+      </c>
+      <c r="D14" s="20">
+        <v>37</v>
+      </c>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+    </row>
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="20">
+        <v>3000</v>
+      </c>
+      <c r="C15" s="20">
+        <v>300</v>
+      </c>
+      <c r="D15" s="20">
+        <v>42</v>
+      </c>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+    </row>
+    <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="20">
+        <v>3500</v>
+      </c>
+      <c r="C16" s="20">
+        <v>350</v>
+      </c>
+      <c r="D16" s="20">
+        <v>47</v>
+      </c>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+    </row>
+    <row r="17" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="20">
+        <v>4000</v>
+      </c>
+      <c r="C17" s="20">
+        <v>400</v>
+      </c>
+      <c r="D17" s="20">
+        <v>52</v>
+      </c>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+    </row>
+    <row r="18" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="20">
+        <v>4500</v>
+      </c>
+      <c r="C18" s="20">
+        <v>450</v>
+      </c>
+      <c r="D18" s="20">
+        <v>57</v>
+      </c>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+    </row>
+    <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="20">
+        <v>5000</v>
+      </c>
+      <c r="C19" s="20">
+        <v>500</v>
+      </c>
+      <c r="D19" s="20">
+        <v>62</v>
+      </c>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+    </row>
+    <row r="20" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="19">
+        <v>1000</v>
+      </c>
+      <c r="C20" s="19">
+        <v>100</v>
+      </c>
+      <c r="D20" s="19">
+        <v>22</v>
+      </c>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+    </row>
+    <row r="21" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="19">
+        <v>1500</v>
+      </c>
+      <c r="C21" s="19">
+        <v>150</v>
+      </c>
+      <c r="D21" s="19">
+        <v>27</v>
+      </c>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+    </row>
+    <row r="22" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="19">
+        <v>2000</v>
+      </c>
+      <c r="C22" s="19">
+        <v>200</v>
+      </c>
+      <c r="D22" s="19">
+        <v>32</v>
+      </c>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+    </row>
+    <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19">
+        <v>2500</v>
+      </c>
+      <c r="C23" s="19">
+        <v>250</v>
+      </c>
+      <c r="D23" s="19">
+        <v>37</v>
+      </c>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+    </row>
+    <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="19">
+        <v>3000</v>
+      </c>
+      <c r="C24" s="19">
+        <v>300</v>
+      </c>
+      <c r="D24" s="19">
+        <v>42</v>
+      </c>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+    </row>
+    <row r="25" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="19">
+        <v>3500</v>
+      </c>
+      <c r="C25" s="19">
+        <v>350</v>
+      </c>
+      <c r="D25" s="19">
+        <v>47</v>
+      </c>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+    </row>
+    <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="19">
+        <v>4000</v>
+      </c>
+      <c r="C26" s="19">
+        <v>400</v>
+      </c>
+      <c r="D26" s="19">
+        <v>52</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+    </row>
+    <row r="27" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="19">
+        <v>4500</v>
+      </c>
+      <c r="C27" s="19">
+        <v>450</v>
+      </c>
+      <c r="D27" s="19">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="19">
+        <v>5000</v>
+      </c>
+      <c r="C28" s="19">
+        <v>500</v>
+      </c>
+      <c r="D28" s="19">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="18">
+        <v>1000</v>
+      </c>
+      <c r="C29" s="18">
+        <v>100</v>
+      </c>
+      <c r="D29" s="18">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="18">
+        <v>1500</v>
+      </c>
+      <c r="C30" s="18">
+        <v>150</v>
+      </c>
+      <c r="D30" s="18">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="18">
+        <v>2000</v>
+      </c>
+      <c r="C31" s="18">
+        <v>200</v>
+      </c>
+      <c r="D31" s="18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" s="18">
+        <v>2500</v>
+      </c>
+      <c r="C32" s="18">
+        <v>250</v>
+      </c>
+      <c r="D32" s="18">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="18">
+        <v>3000</v>
+      </c>
+      <c r="C33" s="18">
+        <v>300</v>
+      </c>
+      <c r="D33" s="18">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="18">
+        <v>3500</v>
+      </c>
+      <c r="C34" s="18">
+        <v>350</v>
+      </c>
+      <c r="D34" s="18">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="18">
+        <v>4000</v>
+      </c>
+      <c r="C35" s="18">
+        <v>400</v>
+      </c>
+      <c r="D35" s="18">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="18">
+        <v>4500</v>
+      </c>
+      <c r="C36" s="18">
+        <v>450</v>
+      </c>
+      <c r="D36" s="18">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="18">
+        <v>5000</v>
+      </c>
+      <c r="C37" s="18">
+        <v>500</v>
+      </c>
+      <c r="D37" s="18">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="21">
+        <v>1000</v>
+      </c>
+      <c r="C38" s="21">
+        <v>100</v>
+      </c>
+      <c r="D38" s="21">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="21">
+        <v>1500</v>
+      </c>
+      <c r="C39" s="21">
+        <v>150</v>
+      </c>
+      <c r="D39" s="21">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="21">
+        <v>2000</v>
+      </c>
+      <c r="C40" s="21">
+        <v>200</v>
+      </c>
+      <c r="D40" s="21">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="21">
+        <v>2500</v>
+      </c>
+      <c r="C41" s="21">
+        <v>250</v>
+      </c>
+      <c r="D41" s="21">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A42" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="21">
+        <v>3000</v>
+      </c>
+      <c r="C42" s="21">
+        <v>300</v>
+      </c>
+      <c r="D42" s="21">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="21">
+        <v>3500</v>
+      </c>
+      <c r="C43" s="21">
+        <v>350</v>
+      </c>
+      <c r="D43" s="21">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="21">
+        <v>4000</v>
+      </c>
+      <c r="C44" s="21">
+        <v>400</v>
+      </c>
+      <c r="D44" s="21">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A45" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="21">
+        <v>4500</v>
+      </c>
+      <c r="C45" s="21">
+        <v>450</v>
+      </c>
+      <c r="D45" s="21">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="21">
+        <v>5000</v>
+      </c>
+      <c r="C46" s="21">
+        <v>500</v>
+      </c>
+      <c r="D46" s="21">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B4:K27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2206,13 +3196,13 @@
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -2413,13 +3403,13 @@
       <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -2620,13 +3610,13 @@
       <c r="B21" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
